--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_07_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_07_18_Cau.xlsx
@@ -643,7 +643,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một `finish_reason` nói về kết thúc bình thường, một về giới hạn output, một về chuyển quyền thực thi hành động.</t>
+          <t>stop (x1) là kết thúc bình thường theo điều kiện dừng (r1); length (x2) là bị cắt do chạm giới hạn token (r2); tool_call (x3) là chuyển sang thực thi/phân phối tool theo contract (r3).</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy ưu tiên metadata thay vì đoán chỉ từ dấu câu cuối.</t>
+          <t>Khi `finish_reason='length'`, câu trả lời chưa kết thúc tự nhiên mà bị cắt do chạm trần token. Ứng dụng phải đánh dấu bị cắt, không trình bày như câu trả lời hoàn chỉnh, và thực hiện retry có điều chỉnh tăng giới hạn token hoặc yêu cầu viết tiếp có kiểm soát.</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bắt đầu ngay trước lời gọi mạng và kết thúc ngay sau khi lời gọi trả về.</t>
+          <t>Để đo độ trễ thuần của lời gọi API, mốc thời gian bắt đầu `start=now()` phải đặt ngay trước lời gọi mạng `response=client.call(req)` và mốc kết thúc tính ngay sau khi lời gọi trả về `elapsed=now()-start`, không kèm bước nạp dữ liệu hay render.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
@@ -829,7 +833,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thời gian trôi qua = thời điểm kết thúc − thời điểm bắt đầu.</t>
+          <t>Độ trễ thuần của lời gọi API = Thời điểm kết thúc − Thời điểm bắt đầu = 13,925 − 12,350 = 1,575 giây.</t>
         </is>
       </c>
     </row>
@@ -879,7 +883,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi instruction nào phải giữ nguyên qua nhiều task của user.</t>
+          <t>'Luôn trả lời như trợ giảng, không tiết lộ secret' (x1) là System content (r1); 'Hãy giải thích attention cho tôi bằng ví dụ' (x2) là User content (r2); 'System message phải xuất hiện trước user message' (x3) là Ràng buộc thứ tự, không phải nội dung yêu cầu của người học (r3).</t>
         </is>
       </c>
     </row>
@@ -961,7 +965,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi lớp trả lời một câu: model hành xử ra sao, user muốn gì, dùng dữ kiện nào và output phải có dạng gì.</t>
+          <t>'Bạn là chuyên viên phân tích...' (x1) là Chỉ dẫn system về cách model hành xử (r1); 'Câu hỏi: Vì sao doanh thu giảm?' (x2) là Input hiện tại của user (r2); 'Bảng doanh thu Q1–Q4' (x3) là Context hỗ trợ (r3); 'Trả JSON gồm cause và evidence_row' (x4) là Hợp đồng output (r4).</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1155,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách đường dẫn content khỏi hai trường thống kê token.</t>
+          <t>choices[0].message.content (x1) tương ứng với result.text (r1); usage.prompt_tokens (x2) tương ứng với metrics.input_tokens (r2); usage.completion_tokens (x3) tương ứng với metrics.output_tokens (r3).</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1249,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo dõi kiểu dữ liệu: text → token ID/tensor → ID được sinh → text.</t>
+          <t>Quy trình suy luận causal language model cục bộ: Nạp tokenizer và causal LM tương thích (o2) -&gt; Tokenize/encode prompt thành tensor (o3) -&gt; Gọi generate với giới hạn output (o4) -&gt; Giải mã (decode) các token ID được sinh thành text (o1).</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1295,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Token ID chỉ có ý nghĩa trong vocabulary mà model đã được huấn luyện.</t>
+          <t>Nạp tokenizer của `model-A` nhưng nạp trọng số của `model-B` khi từ điển khác nhau sẽ dẫn đến việc các token ID bị ánh xạ sai lệch hoàn toàn hoặc vượt quá phạm vi embedding matrix của model, gây lỗi crash hoặc sinh rác.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_07_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_07_18_Cau.xlsx
@@ -718,10 +718,18 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hỏi ai chịu trách nhiệm thực thi hành động và khi nào kết quả quan sát được đưa lại cho model.
-Phân tích theo nguyên lý thiết kế: Hỏi ai chịu trách nhiệm thực thi hành động và khi nào kết quả quan sát được đưa lại cho model.</t>
+- Nhận diện đúng trạng thái (1.5 điểm): Xác định đây là trạng thái trung gian yêu cầu gọi tool, text không phải kết quả cuối.
+- Quy trình xử lý tiếp theo (1.5 điểm): Trình bày đủ 3 bước: trích xuất args -&gt; thực thi tool -&gt; gửi trả message role tool để model tiếp tục sinh.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Trạng thái hệ thống: Yêu cầu chưa hoàn thành; mô hình chưa đưa ra câu trả lời cuối cùng mà đang ở trạng thái Yêu cầu gọi công cụ (Tool Call Request). Đoạn text `'Tôi sẽ kiểm tra lịch'` chỉ là thông điệp phụ trợ/suy nghĩ trung gian, không phải là kết quả trả về cho người dùng.
+- Bước xử lý tiếp theo:
+1. Client phía backend trích xuất tên công cụ và tham số arguments từ `message.tool_calls`.
+2. Backend thực thi hàm cục bộ tương ứng (ví dụ: gọi API kiểm tra lịch trình của người dùng với các đối số nhận được).
+3. Client đóng gói kết quả thực thi thành một message có role `'tool'` kèm `tool_call_id` tương ứng, nối vào lịch sử hội thoại và gửi một request tiếp theo đến mô hình để mô hình đọc kết quả và tạo câu trả lời cuối cùng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: `finish_reason='tool_call'` biểu thị sự chuyển giao quyền kiểm soát (Control Handoff) từ LLM sang môi trường máy chủ. Mô hình không tự thực thi mã mạng; hệ thống runtime phải đảm nhiệm việc điều phối, thực thi công cụ và hoàn trả quan sát (Observation) vào vòng lặp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Documentation - Function Calling Flow (https://platform.openai.com/docs/guides/function-calling); Anthropic Claude - Tool Use Integration.</t>
         </is>
       </c>
     </row>
@@ -796,10 +804,18 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách độ trễ khởi tạo khỏi độ trễ lời gọi trước khi so sánh.
-Phân tích theo nguyên lý thiết kế: Tách độ trễ khởi tạo khỏi độ trễ lời gọi trước khi so sánh.</t>
+- Đánh giá kết luận sai lệch (1.5 điểm): Khẳng định không thể kết luận B nhanh hơn, chỉ ra A có thời gian gọi mạng thuần túy là 0,7s sau khi trừ 0,5s init client.
+- Đề xuất quy trình đo chuẩn (1.5 điểm): Nêu rõ việc warm-up/tái sử dụng client, chỉ đo round-trip của API call và đo lặp lại theo phân vị P50/P95.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Có thể kết luận lời gọi mạng của B nhanh hơn không?: KHÔNG THỂ kết luận. Phép đo của Model A bị cộng dồn thêm 0,5 giây độ trễ của khâu khởi tạo client (bao gồm khởi tạo HTTP session, phân giải DNS lookup, bắt tay TLS handshake và thiết lập connection pool), trong khi Model B tái sử dụng kết nối ấm (warm connection). Nếu loại bỏ 0,5 giây khởi tạo, thời gian gọi mạng thuần túy của A thực tế chỉ là $1,2 - 0,5 = 0,7$ giây, nhanh hơn thời gian 0,9 giây của B.
+2. Sửa quy trình đo để đảm bảo tính khách quan:
+- Khởi tạo và warm-up client trước cho cả hai mô hình (sử dụng connection pooling và keep-alive).
+- Chỉ bấm giờ đo thời gian thực thi của chính hàm API call (từ ngay trước lệnh gửi request đến khi nhận được response hoàn chỉnh).
+- Thực hiện lặp lại tối thiểu 20-30 lần cho mỗi mô hình và so sánh dựa trên các chỉ số phân vị (P50, P95, P99) thay vì một lần đo duy nhất.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong đo kiểm hiệu năng mạng (Benchmarking &amp; Profiling), việc để lẫn chi phí thiết lập kết nối (cold start overhead) vào thời gian xử lý nghiệp vụ sẽ làm sai lệch hoàn toàn kết quả so sánh. Phép đo hợp lệ phải cô lập hoàn toàn thời gian mạng vòng (Round Trip Time) trên các kết nối đã được hâm nóng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Monitoring Distributed Systems &amp; Latency Benchmarks (https://sre.google/sre-book/); High Performance Browser Networking - HTTP Connection Management.</t>
         </is>
       </c>
     </row>
@@ -912,10 +928,29 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Thông tin bền vững đi trước; yêu cầu của lượt này đi sau.
-Phân tích theo nguyên lý thiết kế: Thông tin bền vững đi trước; yêu cầu của lượt này đi sau.</t>
+- Cấu hình message 1 đúng role và nội dung (1.5 điểm): Nêu đúng message 1 có role `'system'` với nội dung persona `Bạn là trợ giảng ngắn gọn`.
+- Cấu hình message 2 đúng role và nội dung (1.5 điểm): Nêu đúng message 2 có role `'user'` với nội dung task `Tóm tắt đoạn văn này` đứng sau message system.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Danh sách hai message chuẩn theo đúng thứ tự và vai trò (role):
+1. Message 1 (System):
+```json
+{
+  "role": "system",
+  "content": "Bạn là trợ giảng ngắn gọn."
+}
+```
+2. Message 2 (User):
+```json
+{
+  "role": "user",
+  "content": "Tóm tắt đoạn văn này: [Nội dung văn bản cần tóm tắt]"
+}
+```
+Thứ tự bắt buộc: Tin nhắn `system` luôn đứng đầu để thiết lập ngữ cảnh định hình persona và phong cách phản hồi bền vững; tiếp theo là tin nhắn `user` chứa nhiệm vụ thực thi cụ thể của lượt tương tác.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Kiến trúc Chat Completion phân cấp rõ ràng mức độ ưu tiên của các chỉ dẫn: Role `system` thiết lập các ràng buộc nền tảng, tông giọng và ranh giới an toàn; role `user` mang tải trọng dữ liệu của tác vụ. Đặt chỉ dẫn hệ thống vào đúng vai trò giúp mô hình phân định ranh giới giữa quy tắc và dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Documentation - Chat Completions Roles Architecture (https://platform.openai.com/docs/guides/chat-completions); Anthropic Claude Messages API.</t>
         </is>
       </c>
     </row>
@@ -1044,10 +1079,35 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết bốn nhãn trước, rồi điền đúng một nhiệm vụ cho mỗi nhãn.
-Phân tích theo nguyên lý thiết kế: Viết bốn nhãn trước, rồi điền đúng một nhiệm vụ cho mỗi nhãn.</t>
+- Lớp 1 - Vai trò/Chỉ dẫn hệ thống (1.0 điểm): Thiết lập rõ persona chuyên viên nhân sự và nguyên tắc trung thực.
+- Lớp 2 - Ngữ cảnh dữ liệu (1.0 điểm): Bọc đoạn trích văn bản chính sách rõ ràng với dấu phân cách.
+- Lớp 3 - Nhiệm vụ người dùng (1.0 điểm): Định vị câu hỏi của nhân viên rõ ràng.
+- Lớp 4 - Hợp đồng đầu ra (1.0 điểm): Quy định định dạng JSON hợp lệ chứa đúng 3 trường bắt buộc: `answer`, `quote`, `uncertainty`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Soạn thảo prompt tuân thủ đầy đủ cấu trúc 4 lớp chuyên nghiệp:
+### LỚP 1: CHỈ DẪN HỆ THỐNG / VAI TRÒ (SYSTEM INSTRUCTION / ROLE)
+Bạn là chuyên viên tư vấn nhân sự nội bộ của công ty. Nhiệm vụ của bạn là giải đáp thắc mắc của nhân viên một cách khách quan, chuẩn xác và trung thực dựa duy nhất trên tài liệu chính sách được cung cấp. Tuyệt đối không suy diễn ngoài văn bản.
+### LỚP 2: NGỮ CẢNH DỮ LIỆU (GROUNDING CONTEXT)
+Dưới đây là đoạn văn bản chính sách nhân sự công ty có hiệu lực hiện hành:
+"""
+{policy_document_content}
+"""
+### LỚP 3: NHIỆM VỤ CỤ THỂ CỦA NGƯỜI DÙNG (USER TASK / INPUT)
+Câu hỏi của nhân viên cần giải đáp:
+"""
+{employee_question}
+"""
+### LỚP 4: HỢP ĐỒNG ĐẦU RA VÀ RÀNG BUỘC (OUTPUT CONTRACT &amp; CONSTRAINTS)
+Bạn bắt buộc phải phản hồi dưới định dạng JSON hợp lệ tuân thủ chính xác schema có đúng ba trường sau, không thêm bất kỳ văn bản giải thích nào ngoài JSON:
+{
+  "answer": "&lt;Câu trả lời trực tiếp, rõ ràng cho câu hỏi của nhân viên&gt;",
+  "quote": "&lt;Trích dẫn nguyên văn câu/đoạn trong văn bản chính sách làm căn cứ xác thực&gt;",
+  "uncertainty": "&lt;Nêu mức độ không chắc chắn hoặc ghi rõ nếu chính sách không đề cập đầy đủ&gt;"
+}
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Cấu trúc 4 lớp (Role -&gt; Context -&gt; Task -&gt; Output Contract) là mẫu thiết kế prompt công nghiệp tiêu chuẩn (Industrial Prompt Engineering Pattern). Phân tách rõ ràng giữa tri thức cơ sở (Context) và quy cách giao tiếp (Output Contract) giúp loại bỏ ảo giác và đảm bảo khả năng tích hợp tự động với các hệ thống backend.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Claude Prompt Engineering Guide - Structuring Prompts (https://docs.anthropic.com/en/docs/build-with-claude/prompt-engineering); LangChain Prompt Design Patterns.</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1256,35 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ghép theo ý nghĩa của từng trường; riêng model ID phải dùng mapping đã cho trong đề.
-Phân tích theo nguyên lý thiết kế: Ghép theo ý nghĩa của từng trường; riêng model ID phải dùng mapping đã cho trong đề.</t>
+- Ánh xạ Request của B chính xác (1.5 điểm): Ghi đúng `model_id: 'b-7'`, `system: 'Trả ngắn'`, `input: 'Giải thích token'`.
+- Ánh xạ Response của B chính xác (1.5 điểm): Ghi đúng `result.text: 'Đơn vị xử lý'`, `metrics.input_tokens: 12`, `metrics.output_tokens: 4`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thực hiện ánh xạ hợp đồng API từ Provider A sang Provider B theo quy tắc đã cho (A:`a-1` ↔ B:`b-7`):
+1. Request của Provider B:
+```json
+{
+  "model_id": "b-7",
+  "system": "Trả ngắn",
+  "input": "Giải thích token"
+}
+```
+2. Các trường Response tương ứng của Provider B:
+```json
+{
+  "result": {
+    "text": "Đơn vị xử lý"
+  },
+  "metrics": {
+    "input_tokens": 12,
+    "output_tokens": 4
+  }
+}
+```
+(Ánh xạ: `choices[0].message.content` -&gt; `result.text` = 'Đơn vị xử lý'; `usage.prompt_tokens` -&gt; `metrics.input_tokens` = 12; `usage.completion_tokens` -&gt; `metrics.output_tokens` = 4).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Đây là mô hình Adapter Pattern trong kiến trúc tích hợp LLM Gateway. Gateway phải đóng vai trò trừu tượng hóa các biến thể schema khác nhau giữa các nhà cung cấp (OpenAI style vs Anthropic/Bedrock style) về một mô hình đối tượng chuẩn thống nhất của doanh nghiệp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Gamma, E., et al. Design Patterns: Elements of Reusable Object-Oriented Software (Adapter Pattern); LiteLLM Provider Mapping Documentation (https://docs.litellm.ai/docs/providers)</t>
         </is>
       </c>
     </row>
@@ -1331,10 +1416,24 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hai chỗ trống nằm ở hai phía của `generate`: text→tensor và ID→text.
-Phân tích theo nguyên lý thiết kế: Hai chỗ trống nằm ở hai phía của `generate`: text→tensor và ID→text.</t>
+- Điền đúng chỗ trống 1 (1.5 điểm): Viết chính xác `tokenizer(prompt, return_tensors="pt")`.
+- Điền đúng chỗ trống 2 (1.5 điểm): Viết chính xác `tokenizer.decode(ids[0], skip_special_tokens=True)`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Điền hai bước còn thiếu trong quy trình suy luận mô hình cục bộ với Hugging Face Transformers:
+1. Chỗ trống 1 (Mã hóa văn bản thành tensor đầu vào):
+```python
+inputs = tokenizer(prompt, return_tensors="pt")
+```
+(Hàm tokenizer nhận chuỗi `prompt`, chuyển đổi thành các token ID và trả về đối tượng từ điển chứa PyTorch tensors `input_ids` và `attention_mask` sẵn sàng nạp vào GPU/CPU).
+2. Chỗ trống 2 (Giải mã token IDs sinh ra thành văn bản tự nhiên):
+```python
+text = tokenizer.decode(ids[0], skip_special_tokens=True)
+```
+(Hàm decode chuyển đổi mảng số nguyên token IDs trở lại thành chuỗi văn bản tự nhiên, tham số `skip_special_tokens=True` giúp loại bỏ các token điều khiển hệ thống như `&lt;|endoftext|&gt;`, `&lt;s&gt;`, `&lt;/s&gt;`).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Vòng đời suy luận LLM cục bộ luôn tuân theo quy trình 3 giai đoạn đối xứng: Tokenize (Text -&gt; Tensor) -&gt; Model Generate (Tensor -&gt; Token IDs) -&gt; Detokenize/Decode (Token IDs -&gt; Text). Việc bỏ qua `skip_special_tokens` sẽ để lộ các ký tự kỹ thuật nội bộ ra giao diện người dùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Hugging Face Transformers Documentation - Generation with LLMs (https://huggingface.co/docs/transformers/generation_strategies); PyTorch Model Inference.</t>
         </is>
       </c>
     </row>
@@ -1363,10 +1462,18 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ khoảng trắng nằm trong delta có nội dung `' chào'`.
-Phân tích theo nguyên lý thiết kế: Giữ khoảng trắng nằm trong delta có nội dung `' chào'`.</t>
+- Ghép đúng chuỗi văn bản hoàn chỉnh (1.5 điểm): Xác định chính xác kết quả ghép là `"Xin chào!"` (bảo toàn khoảng trắng giữa 'Xin' và 'chào').
+- Xác định đúng các chunk cần bỏ qua (1.5 điểm): Nêu rõ việc lọc bỏ chunk `None` và chuỗi rỗng `''`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+- Chuỗi text được ứng dụng phát / ghép thành: `"Xin chào!"`
+Giải thích: Bắt đầu với chuỗi rỗng `""` -&gt; bỏ qua `None` -&gt; cộng `'Xin'` -&gt; bỏ qua `''` -&gt; cộng `' chào'` (giữ nguyên khoảng trắng ở đầu delta) -&gt; cộng `'!'` tạo thành chuỗi hoàn chỉnh chuẩn xác là `"Xin chào!"`.
+- Các chunk bị bỏ qua không ghép vào nội dung:
+1. Chunk có delta là `None`: Đây là chunk rỗng thường xuất hiện ở gói tin đầu tiên (metadata/role) hoặc gói tin cuối cùng báo hiệu kết thúc stream (`finish_reason`).
+2. Chunk có delta là chuỗi rỗng `''`: Không mang tải trọng văn bản mới nên cần bỏ qua để tránh xử lý dư thừa.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Trong xử lý luồng Server-Sent Events (SSE), các delta ký tự được truyền tải từng mảnh nhỏ. Bộ ghép chuỗi (Stream Accumulator) phải bảo toàn tuyệt đối các khoảng trắng dẫn đầu (leading whitespace) trong từng token và lọc bỏ các payload rỗng hoặc tín hiệu điều khiển kỹ thuật (`None`, `""`) để không gây gián đoạn chuỗi hiển thị.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+W3C Server-Sent Events (SSE) Specification (https://html.spec.whatwg.org/multipage/server-sent-events.html); OpenAI API Streaming Guide (https://platform.openai.com/docs/api-reference/streaming)</t>
         </is>
       </c>
     </row>
